--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/6mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/6mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X45"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.58322902778</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>715.8598390819095</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>720.1188749472599</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+        <v>0.245165436</v>
+      </c>
+      <c r="Y2">
+        <v>0.261458948</v>
+      </c>
+      <c r="Z2">
+        <v>0.3584227566691837</v>
+      </c>
+      <c r="AA2">
+        <v>8.146756000000003</v>
+      </c>
+      <c r="AB2">
+        <v>0.04511792631630632</v>
+      </c>
+      <c r="AC2">
+        <v>32.29811147250049</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.58334476852</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>718.8440700157067</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>718.9046521765575</v>
+      </c>
+      <c r="X3">
+        <v>0.245159402</v>
+      </c>
+      <c r="Y3">
+        <v>0.261467224</v>
+      </c>
+      <c r="Z3">
+        <v>0.35842466658318</v>
+      </c>
+      <c r="AA3">
+        <v>8.153911000000001</v>
+      </c>
+      <c r="AB3">
+        <v>0.04508050974790338</v>
+      </c>
+      <c r="AC3">
+        <v>32.40585710556561</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.58346050926</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>718.7062126974262</v>
       </c>
-      <c r="V4">
-        <v>1.684561350695591</v>
-      </c>
-      <c r="W4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.245165436</v>
+      </c>
+      <c r="Y4">
+        <v>0.26146977</v>
+      </c>
+      <c r="Z4">
+        <v>0.35843065107901</v>
+      </c>
+      <c r="AA4">
+        <v>8.152166999999999</v>
+      </c>
+      <c r="AB4">
+        <v>0.04509039517254997</v>
+      </c>
+      <c r="AC4">
+        <v>32.4067471434937</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.58357682871</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>716.6784588416929</v>
       </c>
-      <c r="V5">
-        <v>1.212481071787437</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>32.4658925690079</v>
+      </c>
+      <c r="X5">
+        <v>0.245146386</v>
+      </c>
+      <c r="Y5">
+        <v>0.261468496</v>
+      </c>
+      <c r="Z5">
+        <v>0.3584166918118672</v>
+      </c>
+      <c r="AA5">
+        <v>8.161054999999998</v>
+      </c>
+      <c r="AB5">
+        <v>0.04504203713503721</v>
+      </c>
+      <c r="AC5">
+        <v>32.28065775702877</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.58369256945</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>720.4220593461528</v>
       </c>
-      <c r="V6">
-        <v>1.873964610052631</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.245148926</v>
+      </c>
+      <c r="Y6">
+        <v>0.261474862</v>
+      </c>
+      <c r="Z6">
+        <v>0.3584230731647623</v>
+      </c>
+      <c r="AA6">
+        <v>8.162967999999999</v>
+      </c>
+      <c r="AB6">
+        <v>0.0450327640649919</v>
+      </c>
+      <c r="AC6">
+        <v>32.44259662575089</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.58380888889</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>720.9124677083016</v>
       </c>
-      <c r="V7">
-        <v>2.31595466928788</v>
-      </c>
-      <c r="W7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0.24516861</v>
+      </c>
+      <c r="Y7">
+        <v>0.261472634</v>
+      </c>
+      <c r="Z7">
+        <v>0.3584349113301187</v>
+      </c>
+      <c r="AA7">
+        <v>8.152011999999999</v>
+      </c>
+      <c r="AB7">
+        <v>0.04509171992840649</v>
+      </c>
+      <c r="AC7">
+        <v>32.50718308679912</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.58392520833</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>720.2746091483118</v>
       </c>
-      <c r="V8">
-        <v>0.3339424763490847</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>0.245213696</v>
+      </c>
+      <c r="Y8">
+        <v>0.26147327</v>
+      </c>
+      <c r="Z8">
+        <v>0.3584662154659394</v>
+      </c>
+      <c r="AA8">
+        <v>8.129787</v>
+      </c>
+      <c r="AB8">
+        <v>0.04521269083735383</v>
+      </c>
+      <c r="AC8">
+        <v>32.56555322141849</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.58404094908</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>714.4320413401656</v>
       </c>
-      <c r="V9">
-        <v>3.571610002229801</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.245239096</v>
+      </c>
+      <c r="Y9">
+        <v>0.261472634</v>
+      </c>
+      <c r="Z9">
+        <v>0.3584831272707199</v>
+      </c>
+      <c r="AA9">
+        <v>8.116768999999998</v>
+      </c>
+      <c r="AB9">
+        <v>0.04528369226752882</v>
+      </c>
+      <c r="AC9">
+        <v>32.35212070611048</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.58415726852</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>715.720667036421</v>
       </c>
-      <c r="V10">
-        <v>3.069596703593732</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.245276242</v>
+      </c>
+      <c r="Y10">
+        <v>0.26147359</v>
+      </c>
+      <c r="Z10">
+        <v>0.3585092371991698</v>
+      </c>
+      <c r="AA10">
+        <v>8.098674000000003</v>
+      </c>
+      <c r="AB10">
+        <v>0.04538308628353899</v>
+      </c>
+      <c r="AC10">
+        <v>32.48161278702597</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.58427358796</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>715.1568980008233</v>
       </c>
-      <c r="V11">
-        <v>0.645988762678014</v>
-      </c>
-      <c r="W11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>0.24529815</v>
+      </c>
+      <c r="Y11">
+        <v>0.261472952</v>
+      </c>
+      <c r="Z11">
+        <v>0.358523760748178</v>
+      </c>
+      <c r="AA11">
+        <v>8.087401</v>
+      </c>
+      <c r="AB11">
+        <v>0.04544502804779487</v>
+      </c>
+      <c r="AC11">
+        <v>32.50032528822139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.5843893287</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>718.5146783631559</v>
       </c>
-      <c r="V12">
-        <v>1.798101952109489</v>
-      </c>
-      <c r="W12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.245262272</v>
+      </c>
+      <c r="Y12">
+        <v>0.261478364</v>
+      </c>
+      <c r="Z12">
+        <v>0.3585031616411751</v>
+      </c>
+      <c r="AA12">
+        <v>8.108046000000002</v>
+      </c>
+      <c r="AB12">
+        <v>0.04533244597553658</v>
+      </c>
+      <c r="AC12">
+        <v>32.57202783952781</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.58450564815</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>718.5194511724717</v>
       </c>
-      <c r="V13">
-        <v>1.939994655213071</v>
-      </c>
-      <c r="W13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.245231792</v>
+      </c>
+      <c r="Y13">
+        <v>0.261481864</v>
+      </c>
+      <c r="Z13">
+        <v>0.3584848630116002</v>
+      </c>
+      <c r="AA13">
+        <v>8.125036000000001</v>
+      </c>
+      <c r="AB13">
+        <v>0.04524007367739183</v>
+      </c>
+      <c r="AC13">
+        <v>32.50587290968176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.58462138889</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>718.0216759309432</v>
       </c>
-      <c r="V14">
-        <v>0.2860228338646056</v>
-      </c>
-      <c r="W14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.245239096</v>
+      </c>
+      <c r="Y14">
+        <v>0.261487912</v>
+      </c>
+      <c r="Z14">
+        <v>0.3584942709849308</v>
+      </c>
+      <c r="AA14">
+        <v>8.124407999999995</v>
+      </c>
+      <c r="AB14">
+        <v>0.04524452913634678</v>
+      </c>
+      <c r="AC14">
+        <v>32.4865526371861</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.58473770833</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>717.2145620384728</v>
       </c>
-      <c r="V15">
-        <v>0.6585272303305599</v>
-      </c>
-      <c r="W15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>0.245249572</v>
+      </c>
+      <c r="Y15">
+        <v>0.261498734</v>
+      </c>
+      <c r="Z15">
+        <v>0.3585093310498152</v>
+      </c>
+      <c r="AA15">
+        <v>8.124580999999999</v>
+      </c>
+      <c r="AB15">
+        <v>0.04524542058924466</v>
+      </c>
+      <c r="AC15">
+        <v>32.4506745121616</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.58485402778</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>716.9256886919082</v>
       </c>
-      <c r="V16">
-        <v>0.5680476320836538</v>
-      </c>
-      <c r="W16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>0.245273702</v>
+      </c>
+      <c r="Y16">
+        <v>0.26149587</v>
+      </c>
+      <c r="Z16">
+        <v>0.3585237494502166</v>
+      </c>
+      <c r="AA16">
+        <v>8.111083999999998</v>
+      </c>
+      <c r="AB16">
+        <v>0.04531876878233971</v>
+      </c>
+      <c r="AC16">
+        <v>32.49018951994825</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.58497034722</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>716.4588488582663</v>
       </c>
-      <c r="V17">
-        <v>0.38133311145687</v>
-      </c>
-      <c r="W17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>0.245255606</v>
+      </c>
+      <c r="Y17">
+        <v>0.261493322</v>
+      </c>
+      <c r="Z17">
+        <v>0.3585095113452681</v>
+      </c>
+      <c r="AA17">
+        <v>8.118858000000003</v>
+      </c>
+      <c r="AB17">
+        <v>0.04527577840907544</v>
+      </c>
+      <c r="AC17">
+        <v>32.43823208012814</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.58508666667</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>712.2041830373088</v>
       </c>
-      <c r="V18">
-        <v>2.601689717750808</v>
-      </c>
-      <c r="W18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>0.245273068</v>
+      </c>
+      <c r="Y18">
+        <v>0.261491094</v>
+      </c>
+      <c r="Z18">
+        <v>0.3585198322651754</v>
+      </c>
+      <c r="AA18">
+        <v>8.109013000000004</v>
+      </c>
+      <c r="AB18">
+        <v>0.04532930831382655</v>
+      </c>
+      <c r="AC18">
+        <v>32.28372299529513</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.58520298611</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>719.9247770448164</v>
       </c>
-      <c r="V19">
-        <v>3.867005975150569</v>
-      </c>
-      <c r="W19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>0.245287356</v>
+      </c>
+      <c r="Y19">
+        <v>0.261500644</v>
+      </c>
+      <c r="Z19">
+        <v>0.358536572508141</v>
+      </c>
+      <c r="AA19">
+        <v>8.106643999999996</v>
+      </c>
+      <c r="AB19">
+        <v>0.04534392443805697</v>
+      </c>
+      <c r="AC19">
+        <v>32.64421469140517</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.58531872685</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>719.7533892757982</v>
       </c>
-      <c r="V20">
-        <v>4.408844527904006</v>
-      </c>
-      <c r="W20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>0.24529434</v>
+      </c>
+      <c r="Y20">
+        <v>0.261501916</v>
+      </c>
+      <c r="Z20">
+        <v>0.3585422782709267</v>
+      </c>
+      <c r="AA20">
+        <v>8.103787999999994</v>
+      </c>
+      <c r="AB20">
+        <v>0.04535981455661604</v>
+      </c>
+      <c r="AC20">
+        <v>32.64788026404609</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.5854350463</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>719.9826948269512</v>
       </c>
-      <c r="V21">
-        <v>0.1192401446988488</v>
-      </c>
-      <c r="W21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>0.245266718</v>
+      </c>
+      <c r="Y21">
+        <v>0.26150128</v>
+      </c>
+      <c r="Z21">
+        <v>0.3585229175382376</v>
+      </c>
+      <c r="AA21">
+        <v>8.117280999999998</v>
+      </c>
+      <c r="AB21">
+        <v>0.04528575617987234</v>
+      </c>
+      <c r="AC21">
+        <v>32.60496077166074</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.58555136574</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>715.5240007238632</v>
       </c>
-      <c r="V22">
-        <v>2.51065269282499</v>
-      </c>
-      <c r="W22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>0.245263226</v>
+      </c>
+      <c r="Y22">
+        <v>0.261506372</v>
+      </c>
+      <c r="Z22">
+        <v>0.3585242427291765</v>
+      </c>
+      <c r="AA22">
+        <v>8.121572999999998</v>
+      </c>
+      <c r="AB22">
+        <v>0.04526315045515083</v>
+      </c>
+      <c r="AC22">
+        <v>32.38687049903567</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.58566768518</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>719.1381737479486</v>
       </c>
-      <c r="V23">
-        <v>2.368382556577849</v>
-      </c>
-      <c r="W23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>0.245264178</v>
+      </c>
+      <c r="Y23">
+        <v>0.261503508</v>
+      </c>
+      <c r="Z23">
+        <v>0.3585228050017485</v>
+      </c>
+      <c r="AA23">
+        <v>8.119664999999998</v>
+      </c>
+      <c r="AB23">
+        <v>0.04527309483043889</v>
+      </c>
+      <c r="AC23">
+        <v>32.55761073627951</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.58578400463</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>718.4252920550066</v>
       </c>
-      <c r="V24">
-        <v>1.914329227358754</v>
-      </c>
-      <c r="W24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>0.245234016</v>
+      </c>
+      <c r="Y24">
+        <v>0.26150701</v>
+      </c>
+      <c r="Z24">
+        <v>0.3585047264439178</v>
+      </c>
+      <c r="AA24">
+        <v>8.136496999999999</v>
+      </c>
+      <c r="AB24">
+        <v>0.045181845305327</v>
+      </c>
+      <c r="AC24">
+        <v>32.45978040906368</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.58589974537</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>717.9949084983639</v>
       </c>
-      <c r="V25">
-        <v>0.5774203761651855</v>
-      </c>
-      <c r="W25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>0.245193376</v>
+      </c>
+      <c r="Y25">
+        <v>0.261507964</v>
+      </c>
+      <c r="Z25">
+        <v>0.3584776239456274</v>
+      </c>
+      <c r="AA25">
+        <v>8.157294</v>
+      </c>
+      <c r="AB25">
+        <v>0.04506906423734065</v>
+      </c>
+      <c r="AC25">
+        <v>32.35935865319629</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.58601606482</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>721.1386095029815</v>
       </c>
-      <c r="V26">
-        <v>1.704414737563706</v>
-      </c>
-      <c r="W26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>0.24514702</v>
+      </c>
+      <c r="Y26">
+        <v>0.26149746</v>
+      </c>
+      <c r="Z26">
+        <v>0.3584382554936513</v>
+      </c>
+      <c r="AA26">
+        <v>8.175220000000003</v>
+      </c>
+      <c r="AB26">
+        <v>0.04497041553257262</v>
+      </c>
+      <c r="AC26">
+        <v>32.4299029259307</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.58613180555</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>720.1798462428929</v>
       </c>
-      <c r="V27">
-        <v>1.611212583884104</v>
-      </c>
-      <c r="W27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23">
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>0.245138448</v>
+      </c>
+      <c r="Y27">
+        <v>0.261494596</v>
+      </c>
+      <c r="Z27">
+        <v>0.3584303034413412</v>
+      </c>
+      <c r="AA27">
+        <v>8.178074000000002</v>
+      </c>
+      <c r="AB27">
+        <v>0.04495454982448889</v>
+      </c>
+      <c r="AC27">
+        <v>32.37536078051888</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.586248125</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>721.0472148323443</v>
       </c>
-      <c r="V28">
-        <v>0.5291358119125976</v>
-      </c>
-      <c r="W28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23">
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>0.24515845</v>
+      </c>
+      <c r="Y28">
+        <v>0.26149587</v>
+      </c>
+      <c r="Z28">
+        <v>0.358444912969147</v>
+      </c>
+      <c r="AA28">
+        <v>8.168709999999997</v>
+      </c>
+      <c r="AB28">
+        <v>0.04500527755474391</v>
+      </c>
+      <c r="AC28">
+        <v>32.45093003360471</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.58636444445</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>720.4197766476943</v>
       </c>
-      <c r="V29">
-        <v>0.4478789912237739</v>
-      </c>
-      <c r="W29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23">
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="X29">
+        <v>0.245187342</v>
+      </c>
+      <c r="Y29">
+        <v>0.261501916</v>
+      </c>
+      <c r="Z29">
+        <v>0.3584690847879298</v>
+      </c>
+      <c r="AA29">
+        <v>8.157286999999997</v>
+      </c>
+      <c r="AB29">
+        <v>0.04506808028876415</v>
+      </c>
+      <c r="AC29">
+        <v>32.46793633557183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.58648076389</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>717.9536726451267</v>
       </c>
-      <c r="V30">
-        <v>1.635305827214636</v>
-      </c>
-      <c r="W30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23">
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <v>0.24521052</v>
+      </c>
+      <c r="Y30">
+        <v>0.26150701</v>
+      </c>
+      <c r="Z30">
+        <v>0.3584886544896651</v>
+      </c>
+      <c r="AA30">
+        <v>8.148244999999996</v>
+      </c>
+      <c r="AB30">
+        <v>0.04511797276484329</v>
+      </c>
+      <c r="AC30">
+        <v>32.39261424882204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.58659650463</v>
       </c>
@@ -2618,14 +3104,29 @@
       <c r="U31">
         <v>721.6980062939086</v>
       </c>
-      <c r="V31">
-        <v>1.903311782715591</v>
-      </c>
-      <c r="W31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23">
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>0.245214648</v>
+      </c>
+      <c r="Y31">
+        <v>0.261494596</v>
+      </c>
+      <c r="Z31">
+        <v>0.3584824226248298</v>
+      </c>
+      <c r="AA31">
+        <v>8.139974000000002</v>
+      </c>
+      <c r="AB31">
+        <v>0.04516081939942249</v>
+      </c>
+      <c r="AC31">
+        <v>32.59247332316248</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" s="1">
         <v>46068.58671282407</v>
       </c>
@@ -2689,14 +3190,29 @@
       <c r="U32">
         <v>719.0844131017269</v>
       </c>
-      <c r="V32">
-        <v>1.920480748311531</v>
-      </c>
-      <c r="W32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23">
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>0.245185756</v>
+      </c>
+      <c r="Y32">
+        <v>0.261487912</v>
+      </c>
+      <c r="Z32">
+        <v>0.3584577842193015</v>
+      </c>
+      <c r="AA32">
+        <v>8.151077999999998</v>
+      </c>
+      <c r="AB32">
+        <v>0.04509936897023423</v>
+      </c>
+      <c r="AC32">
+        <v>32.43025326721911</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="1">
         <v>46068.58682914352</v>
       </c>
@@ -2760,14 +3276,29 @@
       <c r="U33">
         <v>718.3040854225108</v>
       </c>
-      <c r="V33">
-        <v>1.77756760501912</v>
-      </c>
-      <c r="W33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23">
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>0.245145432</v>
+      </c>
+      <c r="Y33">
+        <v>0.261479954</v>
+      </c>
+      <c r="Z33">
+        <v>0.3584243981292411</v>
+      </c>
+      <c r="AA33">
+        <v>8.167261000000003</v>
+      </c>
+      <c r="AB33">
+        <v>0.04501041895279082</v>
+      </c>
+      <c r="AC33">
+        <v>32.33116782036846</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="1">
         <v>46068.58694488426</v>
       </c>
@@ -2831,14 +3362,29 @@
       <c r="U34">
         <v>719.841215206719</v>
       </c>
-      <c r="V34">
-        <v>0.7685948961761609</v>
-      </c>
-      <c r="W34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23">
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>0.245150512</v>
+      </c>
+      <c r="Y34">
+        <v>0.261488866</v>
+      </c>
+      <c r="Z34">
+        <v>0.3584343741549185</v>
+      </c>
+      <c r="AA34">
+        <v>8.169176999999998</v>
+      </c>
+      <c r="AB34">
+        <v>0.04500157398599536</v>
+      </c>
+      <c r="AC34">
+        <v>32.39398770429398</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" s="1">
         <v>46068.587060625</v>
       </c>
@@ -2902,14 +3448,29 @@
       <c r="U35">
         <v>722.1433815810341</v>
       </c>
-      <c r="V35">
-        <v>1.932310058857994</v>
-      </c>
-      <c r="W35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23">
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>0.245168292</v>
+      </c>
+      <c r="Y35">
+        <v>0.261493004</v>
+      </c>
+      <c r="Z35">
+        <v>0.3584495536936004</v>
+      </c>
+      <c r="AA35">
+        <v>8.162356000000003</v>
+      </c>
+      <c r="AB35">
+        <v>0.04503913730064497</v>
+      </c>
+      <c r="AC35">
+        <v>32.52471491378025</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" s="1">
         <v>46068.58717636574</v>
       </c>
@@ -2973,14 +3534,29 @@
       <c r="U36">
         <v>720.3429829394391</v>
       </c>
-      <c r="V36">
-        <v>1.210590499253076</v>
-      </c>
-      <c r="W36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23">
+      <c r="V36" t="b">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>0.245187026</v>
+      </c>
+      <c r="Y36">
+        <v>0.26149746</v>
+      </c>
+      <c r="Z36">
+        <v>0.358465618023788</v>
+      </c>
+      <c r="AA36">
+        <v>8.155217</v>
+      </c>
+      <c r="AB36">
+        <v>0.04507854206327086</v>
+      </c>
+      <c r="AC36">
+        <v>32.47201145641751</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29">
       <c r="A37" s="1">
         <v>46068.58729268519</v>
       </c>
@@ -3044,14 +3620,29 @@
       <c r="U37">
         <v>720.0689455793957</v>
       </c>
-      <c r="V37">
-        <v>1.126929195369583</v>
-      </c>
-      <c r="W37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23">
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+      <c r="X37">
+        <v>0.245193692</v>
+      </c>
+      <c r="Y37">
+        <v>0.261502872</v>
+      </c>
+      <c r="Z37">
+        <v>0.3584741255109485</v>
+      </c>
+      <c r="AA37">
+        <v>8.154589999999999</v>
+      </c>
+      <c r="AB37">
+        <v>0.04508285484216744</v>
+      </c>
+      <c r="AC37">
+        <v>32.46276374990846</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
       <c r="A38" s="1">
         <v>46068.58740842593</v>
       </c>
@@ -3115,14 +3706,29 @@
       <c r="U38">
         <v>717.8221366773823</v>
       </c>
-      <c r="V38">
-        <v>1.383107165876441</v>
-      </c>
-      <c r="W38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="X38">
+        <v>0.245207028</v>
+      </c>
+      <c r="Y38">
+        <v>0.261492368</v>
+      </c>
+      <c r="Z38">
+        <v>0.3584755850861258</v>
+      </c>
+      <c r="AA38">
+        <v>8.142670000000003</v>
+      </c>
+      <c r="AB38">
+        <v>0.04514578126756401</v>
+      </c>
+      <c r="AC38">
+        <v>32.40664117145254</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
       <c r="A39" s="1">
         <v>46068.58752416667</v>
       </c>
@@ -3186,14 +3792,29 @@
       <c r="U39">
         <v>721.5584508290883</v>
       </c>
-      <c r="V39">
-        <v>1.88090490505984</v>
-      </c>
-      <c r="W39" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
+      <c r="V39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>0.245206076</v>
+      </c>
+      <c r="Y39">
+        <v>0.261492686</v>
+      </c>
+      <c r="Z39">
+        <v>0.3584751658606387</v>
+      </c>
+      <c r="AA39">
+        <v>8.143305000000005</v>
+      </c>
+      <c r="AB39">
+        <v>0.04514238341195682</v>
+      </c>
+      <c r="AC39">
+        <v>32.57286824146429</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29">
       <c r="A40" s="1">
         <v>46068.58764048611</v>
       </c>
@@ -3257,14 +3878,29 @@
       <c r="U40">
         <v>719.6614499258883</v>
       </c>
-      <c r="V40">
-        <v>1.868231297828298</v>
-      </c>
-      <c r="W40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23">
+      <c r="V40" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>0.245202582</v>
+      </c>
+      <c r="Y40">
+        <v>0.261492686</v>
+      </c>
+      <c r="Z40">
+        <v>0.3584727758853681</v>
+      </c>
+      <c r="AA40">
+        <v>8.145052</v>
+      </c>
+      <c r="AB40">
+        <v>0.04513289004783329</v>
+      </c>
+      <c r="AC40">
+        <v>32.4804010911694</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
       <c r="A41" s="1">
         <v>46068.58775680556</v>
       </c>
@@ -3328,14 +3964,29 @@
       <c r="U41">
         <v>718.9875325685016</v>
       </c>
-      <c r="V41">
-        <v>1.333066498338226</v>
-      </c>
-      <c r="W41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>0.24519401</v>
+      </c>
+      <c r="Y41">
+        <v>0.261502872</v>
+      </c>
+      <c r="Z41">
+        <v>0.3584743430207084</v>
+      </c>
+      <c r="AA41">
+        <v>8.154430999999995</v>
+      </c>
+      <c r="AB41">
+        <v>0.04508371665396196</v>
+      </c>
+      <c r="AC41">
+        <v>32.41463019604957</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" s="1">
         <v>46068.587873125</v>
       </c>
@@ -3399,14 +4050,29 @@
       <c r="U42">
         <v>719.869164284926</v>
       </c>
-      <c r="V42">
-        <v>0.4609020761765795</v>
-      </c>
-      <c r="W42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="X42">
+        <v>0.245175912</v>
+      </c>
+      <c r="Y42">
+        <v>0.26149746</v>
+      </c>
+      <c r="Z42">
+        <v>0.3584580162466496</v>
+      </c>
+      <c r="AA42">
+        <v>8.160774000000004</v>
+      </c>
+      <c r="AB42">
+        <v>0.04504844905830485</v>
+      </c>
+      <c r="AC42">
+        <v>32.42898937593397</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
       <c r="A43" s="1">
         <v>46068.58798886574</v>
       </c>
@@ -3470,14 +4136,29 @@
       <c r="U43">
         <v>724.8536115850295</v>
       </c>
-      <c r="V43">
-        <v>3.163143805327072</v>
-      </c>
-      <c r="W43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="V43" t="b">
+        <v>1</v>
+      </c>
+      <c r="X43">
+        <v>0.245183216</v>
+      </c>
+      <c r="Y43">
+        <v>0.261496506</v>
+      </c>
+      <c r="Z43">
+        <v>0.3584623160923763</v>
+      </c>
+      <c r="AA43">
+        <v>8.156644999999997</v>
+      </c>
+      <c r="AB43">
+        <v>0.04507064375180032</v>
+      </c>
+      <c r="AC43">
+        <v>32.66961889995471</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
       <c r="A44" s="1">
         <v>46068.58810518518</v>
       </c>
@@ -3541,14 +4222,29 @@
       <c r="U44">
         <v>719.4402343428442</v>
       </c>
-      <c r="V44">
-        <v>3.009245446645642</v>
-      </c>
-      <c r="W44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
+      <c r="V44" t="b">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>0.24519274</v>
+      </c>
+      <c r="Y44">
+        <v>0.26148091</v>
+      </c>
+      <c r="Z44">
+        <v>0.3584574536024264</v>
+      </c>
+      <c r="AA44">
+        <v>8.144084999999997</v>
+      </c>
+      <c r="AB44">
+        <v>0.0451361512546849</v>
+      </c>
+      <c r="AC44">
+        <v>32.47276323600457</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
       <c r="A45" s="1">
         <v>46068.58822150463</v>
       </c>
@@ -3612,11 +4308,26 @@
       <c r="U45">
         <v>721.7803180769129</v>
       </c>
-      <c r="V45">
-        <v>2.714951750206928</v>
-      </c>
-      <c r="W45" t="b">
-        <v>1</v>
+      <c r="V45" t="b">
+        <v>1</v>
+      </c>
+      <c r="X45">
+        <v>0.24520671</v>
+      </c>
+      <c r="Y45">
+        <v>0.261483774</v>
+      </c>
+      <c r="Z45">
+        <v>0.3584690986602711</v>
+      </c>
+      <c r="AA45">
+        <v>8.138531999999998</v>
+      </c>
+      <c r="AB45">
+        <v>0.04516683225589875</v>
+      </c>
+      <c r="AC45">
+        <v>32.60053055218917</v>
       </c>
     </row>
   </sheetData>
